--- a/output/pdf_financials_xlsx/AKH.H.xlsx
+++ b/output/pdf_financials_xlsx/AKH.H.xlsx
@@ -2332,31 +2332,31 @@
         <v>0.193658</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.012717</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.00042</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.000804</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.018326</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.027037</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.026775</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.003833</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.024645</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>0</v>
@@ -2365,10 +2365,10 @@
         <v>0</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.006247</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.005664</v>
       </c>
     </row>
     <row r="35">
@@ -2442,31 +2442,31 @@
         <v>0.193658</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.012717</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.00042</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.000804</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.018326</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.027037</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.026775</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.003833</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.024645</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>0</v>
@@ -2475,10 +2475,10 @@
         <v>0</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.006247</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.005664</v>
       </c>
     </row>
     <row r="37">
@@ -3102,31 +3102,31 @@
         <v>0.013355</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.017317</v>
+        <v>0.0046</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.005314</v>
+        <v>0.004894</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.000804</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.018326</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.027037</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.026775</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.003833</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.025895</v>
+        <v>0.00125</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0</v>
@@ -3135,7 +3135,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.006247</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>0</v>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">

--- a/output/pdf_financials_xlsx/AKH.H.xlsx
+++ b/output/pdf_financials_xlsx/AKH.H.xlsx
@@ -6016,7 +6016,7 @@
         <v>-0.013428</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>-0.137279</v>
+        <v>-0.164773</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>0.508954</v>
@@ -6615,16 +6615,16 @@
         <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.012459</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.013283</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.014113</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.002658</v>
       </c>
       <c r="H110" s="3" t="n">
         <v>0</v>
@@ -6667,7 +6667,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.009323</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.009323</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -8027,7 +8027,7 @@
         <v>-0.298334</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-1.336861</v>
+        <v>-1.346184</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-0.596495</v>
@@ -21068,7 +21068,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -22206,7 +22210,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -23160,7 +23168,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -24112,7 +24124,11 @@
           <t>Shares issued for private placement</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -24498,7 +24514,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -26236,7 +26256,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -26522,7 +26546,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
